--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N15" t="n">

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>6.96</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5.94</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>3.32</v>
+        <v>2.83</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.83</v>
+        <v>3.32</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.43</v>
+        <v>1.91</v>
       </c>
       <c r="O17" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="P17" t="n">
-        <v>2.33</v>
+        <v>3.44</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.91</v>
+        <v>2.43</v>
       </c>
       <c r="O18" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>3.44</v>
+        <v>2.33</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.47</v>
+        <v>2.43</v>
       </c>
       <c r="O16" t="n">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="P16" t="n">
-        <v>5.94</v>
+        <v>2.33</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="O17" t="n">
-        <v>3.85</v>
+        <v>4.45</v>
       </c>
       <c r="P17" t="n">
-        <v>3.44</v>
+        <v>5.94</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.43</v>
+        <v>1.91</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="P18" t="n">
-        <v>2.33</v>
+        <v>3.44</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="O17" t="n">
-        <v>4.45</v>
+        <v>3.85</v>
       </c>
       <c r="P17" t="n">
-        <v>5.94</v>
+        <v>3.44</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="O18" t="n">
-        <v>3.85</v>
+        <v>4.45</v>
       </c>
       <c r="P18" t="n">
-        <v>3.44</v>
+        <v>5.94</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.83</v>
+        <v>3.32</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>3.32</v>
+        <v>2.83</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="O17" t="n">
-        <v>3.85</v>
+        <v>4.45</v>
       </c>
       <c r="P17" t="n">
-        <v>3.44</v>
+        <v>5.94</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="O18" t="n">
-        <v>4.45</v>
+        <v>3.85</v>
       </c>
       <c r="P18" t="n">
-        <v>5.94</v>
+        <v>3.44</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="O17" t="n">
-        <v>4.45</v>
+        <v>3.85</v>
       </c>
       <c r="P17" t="n">
-        <v>5.94</v>
+        <v>3.44</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="O18" t="n">
-        <v>3.85</v>
+        <v>4.45</v>
       </c>
       <c r="P18" t="n">
-        <v>3.44</v>
+        <v>5.94</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>3.32</v>
+        <v>2.83</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.83</v>
+        <v>3.32</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.43</v>
+        <v>1.91</v>
       </c>
       <c r="O16" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="P16" t="n">
-        <v>2.33</v>
+        <v>3.44</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2996,10 +2996,10 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="O17" t="n">
-        <v>3.85</v>
+        <v>4.45</v>
       </c>
       <c r="P17" t="n">
-        <v>3.44</v>
+        <v>5.94</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.47</v>
+        <v>2.43</v>
       </c>
       <c r="O18" t="n">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>5.94</v>
+        <v>2.33</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.83</v>
+        <v>3.32</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>3.32</v>
+        <v>2.83</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.91</v>
+        <v>2.43</v>
       </c>
       <c r="O16" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="P16" t="n">
-        <v>3.44</v>
+        <v>2.33</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2996,10 +2996,10 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="O17" t="n">
-        <v>4.45</v>
+        <v>3.85</v>
       </c>
       <c r="P17" t="n">
-        <v>5.94</v>
+        <v>3.44</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.43</v>
+        <v>1.47</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="P18" t="n">
-        <v>2.33</v>
+        <v>5.94</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.43</v>
+        <v>1.47</v>
       </c>
       <c r="O16" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="P16" t="n">
-        <v>2.33</v>
+        <v>5.94</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.47</v>
+        <v>2.43</v>
       </c>
       <c r="O18" t="n">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>5.94</v>
+        <v>2.33</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.47</v>
+        <v>2.43</v>
       </c>
       <c r="O16" t="n">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="P16" t="n">
-        <v>5.94</v>
+        <v>2.33</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.43</v>
+        <v>1.47</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="P18" t="n">
-        <v>2.33</v>
+        <v>5.94</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>3.32</v>
+        <v>2.83</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.83</v>
+        <v>3.32</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.83</v>
+        <v>3.32</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>3.32</v>
+        <v>2.83</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.43</v>
+        <v>1.91</v>
       </c>
       <c r="O16" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="P16" t="n">
-        <v>2.33</v>
+        <v>3.44</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2996,10 +2996,10 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="O17" t="n">
-        <v>3.85</v>
+        <v>4.45</v>
       </c>
       <c r="P17" t="n">
-        <v>3.44</v>
+        <v>5.94</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.47</v>
+        <v>2.43</v>
       </c>
       <c r="O18" t="n">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>5.94</v>
+        <v>2.33</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1211,16 +1211,16 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="O16" t="n">
-        <v>3.85</v>
+        <v>4.45</v>
       </c>
       <c r="P16" t="n">
-        <v>3.44</v>
+        <v>5.94</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2996,10 +2996,10 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="O17" t="n">
-        <v>4.45</v>
+        <v>3.85</v>
       </c>
       <c r="P17" t="n">
-        <v>5.94</v>
+        <v>3.44</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1211,16 +1211,16 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>3.32</v>
+        <v>2.83</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.83</v>
+        <v>3.32</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.47</v>
+        <v>2.43</v>
       </c>
       <c r="O16" t="n">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="P16" t="n">
-        <v>5.94</v>
+        <v>2.33</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="O17" t="n">
-        <v>3.85</v>
+        <v>4.45</v>
       </c>
       <c r="P17" t="n">
-        <v>3.44</v>
+        <v>5.94</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3155,10 +3155,10 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.43</v>
+        <v>1.91</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="P18" t="n">
-        <v>2.33</v>
+        <v>3.44</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.43</v>
+        <v>1.91</v>
       </c>
       <c r="O16" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="P16" t="n">
-        <v>2.33</v>
+        <v>3.44</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2996,10 +2996,10 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.91</v>
+        <v>2.43</v>
       </c>
       <c r="O18" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>3.44</v>
+        <v>2.33</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.83</v>
+        <v>3.32</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>3.32</v>
+        <v>2.83</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.91</v>
+        <v>2.43</v>
       </c>
       <c r="O16" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="P16" t="n">
-        <v>3.44</v>
+        <v>2.33</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2996,10 +2996,10 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.43</v>
+        <v>1.91</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="P18" t="n">
-        <v>2.33</v>
+        <v>3.44</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1370,10 +1370,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2315,19 +2315,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2336,10 +2336,10 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -2348,31 +2348,31 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>3.32</v>
+        <v>2.83</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.83</v>
+        <v>3.32</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1211,10 +1211,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1370,71 +1370,71 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.49</v>
+        <v>2.48</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.68</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>3.95</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,10 +1700,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1847,10 +1847,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,43 +2177,43 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.83</v>
+        <v>3.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>3.32</v>
+        <v>2.83</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2666,31 +2666,31 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.43</v>
+        <v>1.47</v>
       </c>
       <c r="O16" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="P16" t="n">
-        <v>2.33</v>
+        <v>5.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.47</v>
+        <v>2.43</v>
       </c>
       <c r="O17" t="n">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="P17" t="n">
-        <v>5.94</v>
+        <v>2.33</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3278,40 +3278,40 @@
         <v>3.44</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC18" t="n">
         <v>1.8</v>
@@ -3320,13 +3320,13 @@
         <v>1.87</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1847,10 +1847,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,43 +2177,43 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,61 +2951,61 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="O16" t="n">
-        <v>4.45</v>
+        <v>3.85</v>
       </c>
       <c r="P16" t="n">
-        <v>5.94</v>
+        <v>3.44</v>
       </c>
       <c r="Q16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V16" t="n">
         <v>1.83</v>
       </c>
-      <c r="R16" t="n">
+      <c r="W16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB16" t="n">
         <v>3</v>
       </c>
-      <c r="S16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="T16" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V16" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>3.68</v>
-      </c>
       <c r="AC16" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.21</v>
+        <v>1.87</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AG16" t="n">
         <v>3</v>
@@ -3024,7 +3024,7 @@
         <v>1.18</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.38</v>
+        <v>1.65</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,61 +3269,61 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="O18" t="n">
-        <v>3.85</v>
+        <v>4.45</v>
       </c>
       <c r="P18" t="n">
-        <v>3.44</v>
+        <v>5.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="R18" t="n">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T18" t="n">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="U18" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="V18" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>3</v>
+        <v>3.68</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.87</v>
+        <v>2.21</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AG18" t="n">
         <v>3</v>
@@ -3342,7 +3342,7 @@
         <v>1.18</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.65</v>
+        <v>2.38</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1211,71 +1211,71 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.49</v>
+        <v>2.48</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK5" t="n">
         <v>1.68</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>3.95</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1370,22 +1370,22 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.48</v>
+        <v>1.49</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="S6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>2.63</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.68</v>
+        <v>3.95</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,10 +1700,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.72</v>
+        <v>4.04</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P11" t="n">
-        <v>4.33</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -2189,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="O16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V16" t="n">
         <v>1.91</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="P16" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T16" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.83</v>
-      </c>
       <c r="W16" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AB16" t="n">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AG16" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.43</v>
+        <v>1.91</v>
       </c>
       <c r="O17" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="P17" t="n">
-        <v>2.33</v>
+        <v>3.44</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="R17" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="S17" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="T17" t="n">
-        <v>4.8</v>
+        <v>4.15</v>
       </c>
       <c r="U17" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="V17" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="W17" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1211,22 +1211,22 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.48</v>
+        <v>1.49</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="S5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>2.63</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.68</v>
+        <v>3.95</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1370,71 +1370,71 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.49</v>
+        <v>2.48</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.68</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>3.95</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -2189,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.43</v>
+        <v>1.91</v>
       </c>
       <c r="O16" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="P16" t="n">
-        <v>2.33</v>
+        <v>3.44</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="S16" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="T16" t="n">
-        <v>4.8</v>
+        <v>4.15</v>
       </c>
       <c r="U16" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="V16" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="W16" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,61 +3110,61 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="O17" t="n">
-        <v>3.85</v>
+        <v>4.45</v>
       </c>
       <c r="P17" t="n">
-        <v>3.44</v>
+        <v>5.94</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="R17" t="n">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="S17" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T17" t="n">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="U17" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="V17" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>3</v>
+        <v>3.68</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.87</v>
+        <v>2.21</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AG17" t="n">
         <v>3</v>
@@ -3183,7 +3183,7 @@
         <v>1.18</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.65</v>
+        <v>2.38</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.47</v>
+        <v>2.43</v>
       </c>
       <c r="O18" t="n">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>5.94</v>
+        <v>2.33</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="R18" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="S18" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="T18" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="U18" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="V18" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="W18" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z18" t="n">
-        <v>8.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AG18" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.38</v>
+        <v>1.42</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q6" t="n">
         <v>2.48</v>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK6" t="n">
         <v>1.68</v>
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.72</v>
+        <v>5.54</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="P9" t="n">
-        <v>4.33</v>
+        <v>1.47</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,40 +2474,40 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>3.32</v>
+        <v>2.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z13" t="n">
         <v>4.1</v>
@@ -2516,22 +2516,22 @@
         <v>1.64</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,40 +2633,40 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.83</v>
+        <v>3.32</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z14" t="n">
         <v>4.1</v>
@@ -2675,22 +2675,22 @@
         <v>1.64</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="O16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V16" t="n">
         <v>1.91</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="P16" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T16" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.83</v>
-      </c>
       <c r="W16" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AB16" t="n">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AG16" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,61 +3110,61 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="O17" t="n">
-        <v>4.45</v>
+        <v>3.85</v>
       </c>
       <c r="P17" t="n">
-        <v>5.94</v>
+        <v>3.44</v>
       </c>
       <c r="Q17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V17" t="n">
         <v>1.83</v>
       </c>
-      <c r="R17" t="n">
+      <c r="W17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB17" t="n">
         <v>3</v>
       </c>
-      <c r="S17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V17" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>3.68</v>
-      </c>
       <c r="AC17" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.21</v>
+        <v>1.87</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AG17" t="n">
         <v>3</v>
@@ -3183,7 +3183,7 @@
         <v>1.18</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.38</v>
+        <v>1.65</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.43</v>
+        <v>1.47</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="P18" t="n">
-        <v>2.33</v>
+        <v>5.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.88</v>
+        <v>1.83</v>
       </c>
       <c r="R18" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T18" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="U18" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="V18" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.42</v>
+        <v>2.38</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,16 +1679,16 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>4.04</v>
       </c>
       <c r="O8" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="R8" t="n">
         <v>2.28</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V8" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>5.54</v>
+        <v>2.65</v>
       </c>
       <c r="O9" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="P9" t="n">
-        <v>1.47</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="R9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC9" t="n">
         <v>2.63</v>
       </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.16</v>
-      </c>
       <c r="AD9" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.04</v>
+        <v>1.72</v>
       </c>
       <c r="O10" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>4.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.72</v>
+        <v>5.54</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="P11" t="n">
-        <v>4.33</v>
+        <v>1.47</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,43 +2177,43 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.43</v>
+        <v>1.91</v>
       </c>
       <c r="O16" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="P16" t="n">
-        <v>2.33</v>
+        <v>3.44</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="S16" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="T16" t="n">
-        <v>4.8</v>
+        <v>4.15</v>
       </c>
       <c r="U16" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="V16" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="W16" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,61 +3110,61 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="O17" t="n">
-        <v>3.85</v>
+        <v>4.45</v>
       </c>
       <c r="P17" t="n">
-        <v>3.44</v>
+        <v>5.94</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="R17" t="n">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="S17" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T17" t="n">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="U17" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="V17" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>3</v>
+        <v>3.68</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.87</v>
+        <v>2.21</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AG17" t="n">
         <v>3</v>
@@ -3183,7 +3183,7 @@
         <v>1.18</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.65</v>
+        <v>2.38</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.47</v>
+        <v>2.43</v>
       </c>
       <c r="O18" t="n">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>5.94</v>
+        <v>2.33</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="R18" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="S18" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="T18" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="U18" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="V18" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="W18" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z18" t="n">
-        <v>8.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AG18" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.38</v>
+        <v>1.42</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.04</v>
+        <v>1.72</v>
       </c>
       <c r="O8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>4.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,10 +1700,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.72</v>
+        <v>4.04</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P10" t="n">
-        <v>4.33</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,40 +2474,40 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.83</v>
+        <v>3.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z13" t="n">
         <v>4.1</v>
@@ -2516,22 +2516,22 @@
         <v>1.64</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,40 +2633,40 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>3.32</v>
+        <v>2.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z14" t="n">
         <v>4.1</v>
@@ -2675,22 +2675,22 @@
         <v>1.64</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.72</v>
+        <v>5.54</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="P8" t="n">
-        <v>4.33</v>
+        <v>1.47</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,16 +1838,16 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.65</v>
+        <v>4.04</v>
       </c>
       <c r="O9" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="R9" t="n">
         <v>2.28</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V9" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.04</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="R10" t="n">
         <v>2.28</v>
@@ -2018,43 +2018,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5.54</v>
+        <v>1.72</v>
       </c>
       <c r="O11" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>1.47</v>
+        <v>4.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,43 +2177,43 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,40 +2474,40 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>3.32</v>
+        <v>2.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z13" t="n">
         <v>4.1</v>
@@ -2516,22 +2516,22 @@
         <v>1.64</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P14" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE14" t="n">
         <v>1.15</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2801,55 +2801,55 @@
         <v>8.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="R15" t="n">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="S15" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="T15" t="n">
-        <v>3.88</v>
+        <v>5.5</v>
       </c>
       <c r="U15" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="V15" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.9</v>
+        <v>4.35</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2951,34 +2951,34 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="O16" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="P16" t="n">
-        <v>3.44</v>
+        <v>2.6</v>
       </c>
       <c r="Q16" t="n">
         <v>2.5</v>
       </c>
       <c r="R16" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="S16" t="n">
         <v>1.17</v>
       </c>
       <c r="T16" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V16" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
@@ -2987,22 +2987,22 @@
         <v>1.05</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AB16" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AF16" t="n">
         <v>1.31</v>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.47</v>
+        <v>2.7</v>
       </c>
       <c r="O17" t="n">
-        <v>4.45</v>
+        <v>3.7</v>
       </c>
       <c r="P17" t="n">
-        <v>5.94</v>
+        <v>2.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="R17" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="S17" t="n">
         <v>1.15</v>
       </c>
       <c r="T17" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="U17" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="V17" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="W17" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z17" t="n">
-        <v>8.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.21</v>
+        <v>2.02</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AG17" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.43</v>
+        <v>1.48</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="P18" t="n">
-        <v>2.33</v>
+        <v>4.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.88</v>
+        <v>1.86</v>
       </c>
       <c r="R18" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T18" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="U18" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="V18" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.34</v>
+        <v>4.12</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.06</v>
+        <v>2.42</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AF18" t="n">
         <v>1.29</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.42</v>
+        <v>2.38</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="O19" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>6.96</v>
+        <v>5.3</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,16 +1838,16 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.04</v>
+        <v>2.65</v>
       </c>
       <c r="O9" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P9" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="R9" t="n">
         <v>2.28</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>4.04</v>
       </c>
       <c r="O10" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="R10" t="n">
         <v>2.28</v>
@@ -2018,43 +2018,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V10" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P13" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE13" t="n">
         <v>1.15</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE14" t="n">
         <v>1.15</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P16" t="n">
-        <v>2.6</v>
+        <v>2.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="S16" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T16" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="U16" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="W16" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.92</v>
+        <v>3.34</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AG16" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="O17" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P17" t="n">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="R17" t="n">
-        <v>2.78</v>
+        <v>2.55</v>
       </c>
       <c r="S17" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T17" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="U17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V17" t="n">
         <v>1.8</v>
       </c>
-      <c r="V17" t="n">
-        <v>1.91</v>
-      </c>
       <c r="W17" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.34</v>
+        <v>2.92</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.49</v>
+        <v>2.48</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK5" t="n">
         <v>1.68</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>3.95</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.94</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>2.63</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.68</v>
+        <v>3.95</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.04</v>
+        <v>1.72</v>
       </c>
       <c r="O10" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>4.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.72</v>
+        <v>4.04</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P11" t="n">
-        <v>4.33</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -2189,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>1.48</v>
       </c>
       <c r="O16" t="n">
-        <v>3.7</v>
+        <v>4.55</v>
       </c>
       <c r="P16" t="n">
-        <v>2.04</v>
+        <v>4.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>1.86</v>
       </c>
       <c r="R16" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="S16" t="n">
         <v>1.15</v>
       </c>
       <c r="T16" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="U16" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="V16" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.34</v>
+        <v>4.12</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.02</v>
+        <v>2.42</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AF16" t="n">
         <v>1.29</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.44</v>
+        <v>2.38</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.48</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
-        <v>4.55</v>
+        <v>3.7</v>
       </c>
       <c r="P18" t="n">
-        <v>4.8</v>
+        <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.86</v>
+        <v>2.8</v>
       </c>
       <c r="R18" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="S18" t="n">
         <v>1.15</v>
       </c>
       <c r="T18" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="U18" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="V18" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="W18" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z18" t="n">
-        <v>8.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.12</v>
+        <v>3.34</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.42</v>
+        <v>2.02</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AF18" t="n">
         <v>1.29</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,31 +1202,31 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.94</v>
       </c>
-      <c r="O5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>2.63</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.68</v>
+        <v>3.95</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.49</v>
+        <v>2.48</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.68</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>3.95</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5.54</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="P8" t="n">
-        <v>1.47</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="R8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC8" t="n">
         <v>2.63</v>
       </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.16</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.65</v>
+        <v>5.54</v>
       </c>
       <c r="O9" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>1.47</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.28</v>
+        <v>2.63</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="W9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.11</v>
       </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z9" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.63</v>
+        <v>2.16</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.41</v>
+        <v>1.11</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.72</v>
+        <v>4.04</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P10" t="n">
-        <v>4.33</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4.04</v>
+        <v>1.72</v>
       </c>
       <c r="O11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>4.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -2189,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE13" t="n">
         <v>1.15</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P14" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE14" t="n">
         <v>1.15</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.48</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
-        <v>4.55</v>
+        <v>3.7</v>
       </c>
       <c r="P16" t="n">
-        <v>4.8</v>
+        <v>2.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.86</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="S16" t="n">
         <v>1.15</v>
       </c>
       <c r="T16" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="U16" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="V16" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="W16" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.12</v>
+        <v>3.34</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.42</v>
+        <v>2.02</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AF16" t="n">
         <v>1.29</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>1.48</v>
       </c>
       <c r="O18" t="n">
-        <v>3.7</v>
+        <v>4.55</v>
       </c>
       <c r="P18" t="n">
-        <v>2.04</v>
+        <v>4.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.8</v>
+        <v>1.86</v>
       </c>
       <c r="R18" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="S18" t="n">
         <v>1.15</v>
       </c>
       <c r="T18" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="U18" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="V18" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.34</v>
+        <v>4.12</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.02</v>
+        <v>2.42</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AF18" t="n">
         <v>1.29</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.44</v>
+        <v>2.38</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AK5" t="n">
         <v>3.95</v>
@@ -2807,10 +2807,10 @@
         <v>3.25</v>
       </c>
       <c r="S15" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="T15" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="U15" t="n">
         <v>1.62</v>
@@ -2819,13 +2819,13 @@
         <v>2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z15" t="n">
         <v>7.2</v>
@@ -2834,16 +2834,16 @@
         <v>1.23</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.35</v>
+        <v>3.55</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AD15" t="n">
         <v>2.35</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AF15" t="n">
         <v>1.57</v>
@@ -2865,7 +2865,7 @@
         <v>1.06</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.2</v>
+        <v>1.48</v>
       </c>
       <c r="O17" t="n">
-        <v>3.75</v>
+        <v>4.55</v>
       </c>
       <c r="P17" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.5</v>
+        <v>1.86</v>
       </c>
       <c r="R17" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="S17" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T17" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="U17" t="n">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="W17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.18</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK17" t="n">
-        <v>1.56</v>
+        <v>2.38</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,65 +3269,65 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.48</v>
+        <v>2.2</v>
       </c>
       <c r="O18" t="n">
-        <v>4.55</v>
+        <v>3.75</v>
       </c>
       <c r="P18" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.86</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AG18" t="n">
         <v>3</v>
       </c>
-      <c r="S18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="T18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V18" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.38</v>
+        <v>1.56</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>1.72</v>
       </c>
       <c r="O8" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.04</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="R10" t="n">
         <v>2.28</v>
@@ -2018,43 +2018,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.72</v>
+        <v>4.04</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P11" t="n">
-        <v>4.33</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -2189,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG13" t="n">
         <v>2.3</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.28</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE14" t="n">
         <v>1.15</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>1.45</v>
       </c>
       <c r="O16" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.04</v>
+        <v>5.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>1.96</v>
       </c>
       <c r="R16" t="n">
-        <v>2.78</v>
+        <v>3.12</v>
       </c>
       <c r="S16" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="T16" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="V16" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.34</v>
+        <v>3.74</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.44</v>
+        <v>2.6</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.48</v>
+        <v>2.85</v>
       </c>
       <c r="O17" t="n">
-        <v>4.55</v>
+        <v>4.3</v>
       </c>
       <c r="P17" t="n">
-        <v>4.8</v>
+        <v>1.96</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.86</v>
+        <v>2.8</v>
       </c>
       <c r="R17" t="n">
-        <v>3</v>
+        <v>2.53</v>
       </c>
       <c r="S17" t="n">
         <v>1.15</v>
       </c>
       <c r="T17" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="U17" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="V17" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="W17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z17" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.12</v>
+        <v>3.64</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.42</v>
+        <v>2.09</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AF17" t="n">
         <v>1.29</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3269,31 +3269,31 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="O18" t="n">
         <v>3.75</v>
       </c>
       <c r="P18" t="n">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="R18" t="n">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="S18" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T18" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="U18" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="V18" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="W18" t="n">
         <v>1.18</v>
@@ -3308,19 +3308,19 @@
         <v>6.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AB18" t="n">
         <v>2.92</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AD18" t="n">
         <v>1.88</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AF18" t="n">
         <v>1.31</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.49</v>
+        <v>2.48</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK5" t="n">
         <v>1.68</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>3.95</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.94</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>2.63</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.68</v>
+        <v>3.95</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.72</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P8" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>5.54</v>
+        <v>4.04</v>
       </c>
       <c r="O9" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="P9" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="R9" t="n">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="V9" t="n">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.11</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>1.72</v>
       </c>
       <c r="O10" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,43 +2018,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4.04</v>
+        <v>5.54</v>
       </c>
       <c r="O11" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>2.28</v>
+        <v>2.63</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,43 +2177,43 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="V11" t="n">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.98</v>
+        <v>2.48</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.7</v>
+        <v>2.16</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.45</v>
+        <v>2.12</v>
       </c>
       <c r="O16" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="P16" t="n">
-        <v>5.7</v>
+        <v>2.39</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.96</v>
+        <v>2.7</v>
       </c>
       <c r="R16" t="n">
-        <v>3.12</v>
+        <v>2.41</v>
       </c>
       <c r="S16" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="T16" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="V16" t="n">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="W16" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.74</v>
+        <v>2.92</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.52</v>
+        <v>1.91</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.24</v>
+        <v>1.88</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AF16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.2</v>
       </c>
-      <c r="AG16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AK16" t="n">
-        <v>2.6</v>
+        <v>1.56</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.85</v>
+        <v>1.45</v>
       </c>
       <c r="O17" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1.96</v>
       </c>
-      <c r="Q17" t="n">
-        <v>2.8</v>
-      </c>
       <c r="R17" t="n">
-        <v>2.53</v>
+        <v>3.12</v>
       </c>
       <c r="S17" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="T17" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="V17" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.64</v>
+        <v>3.74</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.09</v>
+        <v>2.24</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.44</v>
+        <v>2.6</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.12</v>
+        <v>2.85</v>
       </c>
       <c r="O18" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.39</v>
+        <v>1.96</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R18" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="S18" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="T18" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="U18" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="V18" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="W18" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.92</v>
+        <v>3.64</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.88</v>
+        <v>2.09</v>
       </c>
       <c r="AE18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF18" t="n">
         <v>1.29</v>
       </c>
-      <c r="AF18" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AG18" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,31 +1202,31 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.94</v>
       </c>
-      <c r="O5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>2.63</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.68</v>
+        <v>3.95</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.49</v>
+        <v>2.48</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.68</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>3.95</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>1.72</v>
       </c>
       <c r="O8" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,16 +1838,16 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.04</v>
+        <v>2.65</v>
       </c>
       <c r="O9" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P9" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="R9" t="n">
         <v>2.28</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.72</v>
+        <v>4.04</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P10" t="n">
-        <v>4.33</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2801,16 +2801,16 @@
         <v>8.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="R15" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="S15" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T15" t="n">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="U15" t="n">
         <v>1.62</v>
@@ -2819,13 +2819,13 @@
         <v>2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z15" t="n">
         <v>7.2</v>
@@ -2834,22 +2834,22 @@
         <v>1.23</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.35</v>
+        <v>2.14</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>1.06</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.45</v>
+        <v>3.86</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.12</v>
+        <v>2.85</v>
       </c>
       <c r="O16" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.39</v>
+        <v>1.96</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="S16" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="T16" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="U16" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="V16" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="W16" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.92</v>
+        <v>3.64</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.88</v>
+        <v>2.09</v>
       </c>
       <c r="AE16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.29</v>
       </c>
-      <c r="AF16" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AG16" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.85</v>
+        <v>2.12</v>
       </c>
       <c r="O18" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="P18" t="n">
-        <v>1.96</v>
+        <v>2.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R18" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="S18" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="T18" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="U18" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="V18" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="W18" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.64</v>
+        <v>2.92</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.09</v>
+        <v>1.88</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3431,10 +3431,10 @@
         <v>1.53</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="P19" t="n">
-        <v>5.5</v>
+        <v>6.15</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.49</v>
+        <v>2.48</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK5" t="n">
         <v>1.68</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>3.95</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.94</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>2.63</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.68</v>
+        <v>3.95</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.72</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P8" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,16 +1838,16 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.65</v>
+        <v>4.04</v>
       </c>
       <c r="O9" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="R9" t="n">
         <v>2.28</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V9" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.04</v>
+        <v>1.72</v>
       </c>
       <c r="O10" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>4.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="P15" t="n">
-        <v>8.5</v>
+        <v>13.2</v>
       </c>
       <c r="Q15" t="n">
         <v>1.53</v>
@@ -2816,7 +2816,7 @@
         <v>1.62</v>
       </c>
       <c r="V15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="W15" t="n">
         <v>1.31</v>
@@ -2837,7 +2837,7 @@
         <v>4</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AD15" t="n">
         <v>2.14</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.85</v>
+        <v>2.12</v>
       </c>
       <c r="O16" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="P16" t="n">
-        <v>1.96</v>
+        <v>2.39</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R16" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="S16" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="T16" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="V16" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="W16" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.64</v>
+        <v>2.92</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.09</v>
+        <v>1.88</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.12</v>
+        <v>2.85</v>
       </c>
       <c r="O18" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.39</v>
+        <v>1.96</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R18" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="S18" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="T18" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="U18" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="V18" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="W18" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.92</v>
+        <v>3.64</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.88</v>
+        <v>2.09</v>
       </c>
       <c r="AE18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF18" t="n">
         <v>1.29</v>
       </c>
-      <c r="AF18" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AG18" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK5" t="n">
         <v>1.68</v>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
         <v>3.95</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>5.54</v>
       </c>
       <c r="O8" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>1.47</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>2.28</v>
+        <v>2.63</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="W8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.11</v>
       </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z8" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.63</v>
+        <v>2.16</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.41</v>
+        <v>1.11</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.04</v>
+        <v>1.72</v>
       </c>
       <c r="O9" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>1.78</v>
+        <v>4.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.72</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P10" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,43 +2018,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5.54</v>
+        <v>4.04</v>
       </c>
       <c r="O11" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="P11" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="R11" t="n">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,43 +2177,43 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.11</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
         <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE14" t="n">
         <v>1.15</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2801,7 +2801,7 @@
         <v>13.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="R15" t="n">
         <v>2.85</v>
@@ -2834,10 +2834,10 @@
         <v>1.23</v>
       </c>
       <c r="AB15" t="n">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AD15" t="n">
         <v>2.14</v>
@@ -2865,7 +2865,7 @@
         <v>1.06</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.86</v>
+        <v>3.45</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.12</v>
+        <v>1.35</v>
       </c>
       <c r="O16" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="P16" t="n">
-        <v>2.39</v>
+        <v>4.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="R16" t="n">
-        <v>2.41</v>
+        <v>3.12</v>
       </c>
       <c r="S16" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="T16" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="V16" t="n">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="W16" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.92</v>
+        <v>4</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.91</v>
+        <v>1.52</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.88</v>
+        <v>2.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.29</v>
+        <v>1.61</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AG16" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.56</v>
+        <v>2.06</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.45</v>
+        <v>2.16</v>
       </c>
       <c r="O17" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
-        <v>5.7</v>
+        <v>2.39</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.96</v>
+        <v>2.7</v>
       </c>
       <c r="R17" t="n">
-        <v>3.12</v>
+        <v>2.55</v>
       </c>
       <c r="S17" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="T17" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.68</v>
+        <v>1.97</v>
       </c>
       <c r="V17" t="n">
-        <v>2.02</v>
+        <v>1.66</v>
       </c>
       <c r="W17" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="Z17" t="n">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.74</v>
+        <v>2.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.24</v>
+        <v>1.88</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.61</v>
+        <v>1.26</v>
       </c>
       <c r="AF17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.2</v>
       </c>
-      <c r="AG17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AK17" t="n">
-        <v>2.6</v>
+        <v>1.56</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3269,19 +3269,19 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="O18" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="P18" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.8</v>
+        <v>3.27</v>
       </c>
       <c r="R18" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="S18" t="n">
         <v>1.15</v>
@@ -3290,13 +3290,13 @@
         <v>4.8</v>
       </c>
       <c r="U18" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="V18" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="W18" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
@@ -3308,16 +3308,16 @@
         <v>7.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.64</v>
+        <v>3.35</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AE18" t="n">
         <v>1.43</v>
@@ -3326,7 +3326,7 @@
         <v>1.29</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="O19" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="P19" t="n">
-        <v>6.15</v>
+        <v>5.5</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5.54</v>
+        <v>1.72</v>
       </c>
       <c r="O8" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>1.47</v>
+        <v>4.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.72</v>
+        <v>5.54</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="P9" t="n">
-        <v>4.33</v>
+        <v>1.47</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>4.04</v>
       </c>
       <c r="O10" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="R10" t="n">
         <v>2.28</v>
@@ -2018,43 +2018,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V10" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,16 +2156,16 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4.04</v>
+        <v>2.65</v>
       </c>
       <c r="O11" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="R11" t="n">
         <v>2.28</v>
@@ -2177,43 +2177,43 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="O13" t="n">
         <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE13" t="n">
         <v>1.15</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
         <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE14" t="n">
         <v>1.15</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2951,31 +2951,31 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="O16" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="P16" t="n">
-        <v>4.35</v>
+        <v>5.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="R16" t="n">
-        <v>3.12</v>
+        <v>2.66</v>
       </c>
       <c r="S16" t="n">
         <v>1.15</v>
       </c>
       <c r="T16" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="U16" t="n">
         <v>1.66</v>
       </c>
       <c r="V16" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="W16" t="n">
         <v>1.28</v>
@@ -2990,19 +2990,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AB16" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="AC16" t="n">
         <v>1.52</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AF16" t="n">
         <v>1.3</v>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.06</v>
+        <v>2.43</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,49 +3110,49 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="R17" t="n">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="S17" t="n">
         <v>1.18</v>
       </c>
       <c r="T17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="V17" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC17" t="n">
         <v>1.88</v>
@@ -3167,7 +3167,7 @@
         <v>1.31</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="O18" t="n">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="P18" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
         <v>3.27</v>
@@ -3290,13 +3290,13 @@
         <v>4.8</v>
       </c>
       <c r="U18" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="V18" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="W18" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
@@ -3305,10 +3305,10 @@
         <v>1.03</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AB18" t="n">
         <v>3.35</v>
@@ -3317,16 +3317,16 @@
         <v>1.65</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="AE18" t="n">
         <v>1.43</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,31 +1202,31 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.94</v>
       </c>
-      <c r="O5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>2.63</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.68</v>
+        <v>3.95</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.49</v>
+        <v>2.48</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.68</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>3.95</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.72</v>
+        <v>5.54</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="P8" t="n">
-        <v>4.33</v>
+        <v>1.47</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>5.54</v>
+        <v>1.72</v>
       </c>
       <c r="O9" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>1.47</v>
+        <v>4.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.04</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="R10" t="n">
         <v>2.28</v>
@@ -2018,43 +2018,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,16 +2156,16 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.65</v>
+        <v>4.04</v>
       </c>
       <c r="O11" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="R11" t="n">
         <v>2.28</v>
@@ -2177,43 +2177,43 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
         <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE13" t="n">
         <v>1.15</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
         <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE14" t="n">
         <v>1.15</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
-        <v>13.2</v>
+        <v>8.5</v>
       </c>
       <c r="Q15" t="n">
         <v>1.58</v>
@@ -2807,19 +2807,19 @@
         <v>2.85</v>
       </c>
       <c r="S15" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="U15" t="n">
         <v>1.62</v>
       </c>
       <c r="V15" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
@@ -2834,10 +2834,10 @@
         <v>1.23</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AD15" t="n">
         <v>2.14</v>
@@ -2846,10 +2846,10 @@
         <v>1.49</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.45</v>
+        <v>3.82</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="O16" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>5.7</v>
+        <v>2.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="S16" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="T16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="V16" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.43</v>
+        <v>1.57</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.2</v>
+        <v>1.45</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.63</v>
+        <v>5.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="R17" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="S17" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="T17" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="W17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA17" t="n">
         <v>1.22</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AB17" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.88</v>
+        <v>1.52</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.88</v>
+        <v>2.12</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.57</v>
+        <v>2.43</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.49</v>
+        <v>2.48</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK5" t="n">
         <v>1.68</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>3.95</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="P6" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.94</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>2.63</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.68</v>
+        <v>3.95</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>5.04</v>
+        <v>5</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5.54</v>
+        <v>4.04</v>
       </c>
       <c r="O8" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="P8" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="R8" t="n">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="V8" t="n">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.11</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.72</v>
+        <v>2.65</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P9" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>5.54</v>
       </c>
       <c r="O10" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>1.47</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.28</v>
+        <v>2.63</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,43 +2018,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="W10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.11</v>
       </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z10" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.63</v>
+        <v>2.16</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.41</v>
+        <v>1.11</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4.04</v>
+        <v>1.72</v>
       </c>
       <c r="O11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>4.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -2189,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="P14" t="n">
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="R14" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="S14" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U14" t="n">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="V14" t="n">
         <v>1.51</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
         <v>1.04</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.18</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.15</v>
       </c>
       <c r="AF14" t="n">
         <v>1.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK14" t="n">
         <v>1.65</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.45</v>
+        <v>2.89</v>
       </c>
       <c r="O17" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P17" t="n">
-        <v>5.7</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.83</v>
+        <v>3.27</v>
       </c>
       <c r="R17" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="S17" t="n">
         <v>1.15</v>
       </c>
       <c r="T17" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="U17" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="V17" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="W17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z17" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.43</v>
+        <v>1.32</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.89</v>
+        <v>1.45</v>
       </c>
       <c r="O18" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.05</v>
+        <v>5.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.27</v>
+        <v>1.83</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="S18" t="n">
         <v>1.15</v>
       </c>
       <c r="T18" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="U18" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="V18" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.32</v>
+        <v>2.43</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,31 +1202,31 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.94</v>
       </c>
-      <c r="O5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>2.63</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.68</v>
+        <v>3.95</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.15</v>
+        <v>1.94</v>
       </c>
       <c r="O6" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>13</v>
+        <v>3.54</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.49</v>
+        <v>2.48</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.68</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>3.95</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.04</v>
+        <v>1.69</v>
       </c>
       <c r="O8" t="n">
         <v>3.55</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>4.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,10 +1700,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.72</v>
+        <v>4.04</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P11" t="n">
-        <v>4.33</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -2189,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="P14" t="n">
         <v>3</v>
@@ -2669,7 +2669,7 @@
         <v>1.16</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AA14" t="n">
         <v>1.64</v>
@@ -2801,10 +2801,10 @@
         <v>8.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="R15" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="S15" t="n">
         <v>1.14</v>
@@ -2837,13 +2837,13 @@
         <v>4</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AF15" t="n">
         <v>1.57</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.2</v>
+        <v>1.35</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.63</v>
+        <v>5.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="R16" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="S16" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="T16" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="W16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.22</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AB16" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.88</v>
+        <v>1.52</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AG16" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.57</v>
+        <v>2.43</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.89</v>
+        <v>2.2</v>
       </c>
       <c r="O17" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.27</v>
+        <v>2.5</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="S17" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="T17" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="V17" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="W17" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.11</v>
+        <v>1.88</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.45</v>
+        <v>2.53</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="P18" t="n">
-        <v>5.7</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.83</v>
+        <v>3.27</v>
       </c>
       <c r="R18" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="S18" t="n">
         <v>1.15</v>
       </c>
       <c r="T18" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="U18" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="V18" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="W18" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z18" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AE18" t="n">
         <v>1.48</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.43</v>
+        <v>1.32</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="O19" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.15</v>
+        <v>1.94</v>
       </c>
       <c r="O5" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>13</v>
+        <v>3.54</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.49</v>
+        <v>2.48</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK5" t="n">
         <v>1.68</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>3.95</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="P6" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.94</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>2.63</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.68</v>
+        <v>3.95</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.69</v>
+        <v>4.04</v>
       </c>
       <c r="O8" t="n">
         <v>3.55</v>
       </c>
       <c r="P8" t="n">
-        <v>4.2</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,10 +1700,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>5.54</v>
+        <v>1.69</v>
       </c>
       <c r="O10" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="P10" t="n">
-        <v>1.47</v>
+        <v>4.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,43 +2018,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4.04</v>
+        <v>5.54</v>
       </c>
       <c r="O11" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>2.28</v>
+        <v>2.63</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,43 +2177,43 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="V11" t="n">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.98</v>
+        <v>2.48</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.7</v>
+        <v>2.16</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.79</v>
+        <v>1.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,40 +2474,40 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P13" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z13" t="n">
         <v>4.1</v>
@@ -2516,22 +2516,22 @@
         <v>1.64</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,40 +2633,40 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z14" t="n">
         <v>4.1</v>
@@ -2675,22 +2675,22 @@
         <v>1.64</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.35</v>
+        <v>2.2</v>
       </c>
       <c r="O16" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>5.7</v>
+        <v>2.39</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="S16" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="T16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="V16" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="W16" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.43</v>
+        <v>1.57</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,65 +3110,65 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.2</v>
+        <v>1.35</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.39</v>
+        <v>5.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="R17" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="S17" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="T17" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="V17" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AB17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AG17" t="n">
         <v>3.25</v>
       </c>
-      <c r="AC17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.57</v>
+        <v>2.43</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,31 +1202,31 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.94</v>
       </c>
-      <c r="O5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>2.63</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.68</v>
+        <v>3.95</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.15</v>
+        <v>1.94</v>
       </c>
       <c r="O6" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>13</v>
+        <v>3.54</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.49</v>
+        <v>2.48</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.68</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>3.95</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.04</v>
+        <v>1.69</v>
       </c>
       <c r="O8" t="n">
         <v>3.55</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>4.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,10 +1700,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.69</v>
+        <v>4.04</v>
       </c>
       <c r="O10" t="n">
         <v>3.55</v>
       </c>
       <c r="P10" t="n">
-        <v>4.2</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="P16" t="n">
-        <v>2.39</v>
+        <v>1.93</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.5</v>
+        <v>3.27</v>
       </c>
       <c r="R16" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="S16" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="T16" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U16" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="V16" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="O18" t="n">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>1.91</v>
+        <v>2.39</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.27</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="S18" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="T18" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="V18" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="W18" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.11</v>
+        <v>1.88</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P19" t="n">
         <v>6</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.15</v>
+        <v>1.94</v>
       </c>
       <c r="O5" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>13</v>
+        <v>3.54</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.49</v>
+        <v>2.48</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK5" t="n">
         <v>1.68</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>3.95</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="P6" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.94</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>2.63</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.68</v>
+        <v>3.95</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.69</v>
+        <v>5.54</v>
       </c>
       <c r="O8" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="P8" t="n">
-        <v>4.2</v>
+        <v>1.47</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.65</v>
+        <v>1.69</v>
       </c>
       <c r="O9" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.04</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="R10" t="n">
         <v>2.28</v>
@@ -2018,43 +2018,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.79</v>
+        <v>1.26</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5.54</v>
+        <v>4.04</v>
       </c>
       <c r="O11" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="P11" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="R11" t="n">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,43 +2177,43 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.11</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,40 +2474,40 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z13" t="n">
         <v>4.1</v>
@@ -2516,22 +2516,22 @@
         <v>1.64</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,40 +2633,40 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P14" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z14" t="n">
         <v>4.1</v>
@@ -2675,22 +2675,22 @@
         <v>1.64</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2804,16 +2804,16 @@
         <v>1.53</v>
       </c>
       <c r="R15" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="S15" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T15" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="U15" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="V15" t="n">
         <v>2</v>
@@ -2834,16 +2834,16 @@
         <v>1.23</v>
       </c>
       <c r="AB15" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="AC15" t="n">
         <v>1.63</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AF15" t="n">
         <v>1.57</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="O16" t="n">
-        <v>3.88</v>
+        <v>4.2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.93</v>
+        <v>5.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.27</v>
+        <v>1.83</v>
       </c>
       <c r="R16" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="S16" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T16" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="V16" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="AE16" t="n">
         <v>1.48</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.32</v>
+        <v>2.43</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="O17" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z17" t="n">
         <v>4.2</v>
       </c>
-      <c r="P17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AA17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="AE17" t="n">
         <v>1.48</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.43</v>
+        <v>1.32</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>3.54</v>
+        <v>3.45</v>
       </c>
       <c r="Q5" t="n">
         <v>2.48</v>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
         <v>1.68</v>
@@ -1523,10 +1523,10 @@
         <v>1.58</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5.54</v>
+        <v>1.69</v>
       </c>
       <c r="O8" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="P8" t="n">
-        <v>1.47</v>
+        <v>4.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.69</v>
+        <v>4.04</v>
       </c>
       <c r="O9" t="n">
         <v>3.55</v>
       </c>
       <c r="P9" t="n">
-        <v>4.2</v>
+        <v>1.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>5.54</v>
       </c>
       <c r="O10" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>1.47</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.28</v>
+        <v>2.63</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,43 +2018,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="W10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.11</v>
       </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z10" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.63</v>
+        <v>2.16</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.41</v>
+        <v>1.11</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,16 +2156,16 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4.04</v>
+        <v>2.65</v>
       </c>
       <c r="O11" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="R11" t="n">
         <v>2.28</v>
@@ -2177,43 +2177,43 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.79</v>
+        <v>1.26</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="O12" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="P12" t="n">
-        <v>5.53</v>
+        <v>5.35</v>
       </c>
       <c r="Q12" t="n">
         <v>1.98</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.35</v>
+        <v>2.2</v>
       </c>
       <c r="O16" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>5.7</v>
+        <v>2.39</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="S16" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="T16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.66</v>
+        <v>1.97</v>
       </c>
       <c r="V16" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="W16" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.43</v>
+        <v>1.57</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="O17" t="n">
-        <v>3.88</v>
+        <v>4.2</v>
       </c>
       <c r="P17" t="n">
-        <v>1.93</v>
+        <v>5.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.27</v>
+        <v>1.83</v>
       </c>
       <c r="R17" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="S17" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T17" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="V17" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="AE17" t="n">
         <v>1.48</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.32</v>
+        <v>2.43</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="P18" t="n">
-        <v>2.39</v>
+        <v>1.93</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.5</v>
+        <v>3.27</v>
       </c>
       <c r="R18" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="S18" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="T18" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U18" t="n">
-        <v>1.97</v>
+        <v>1.79</v>
       </c>
       <c r="V18" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,31 +1202,31 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.89</v>
+        <v>1.15</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="P5" t="n">
-        <v>3.45</v>
+        <v>13</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.48</v>
+        <v>1.49</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="S5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>2.63</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.68</v>
+        <v>3.95</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.15</v>
+        <v>1.89</v>
       </c>
       <c r="O6" t="n">
-        <v>6.6</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>13</v>
+        <v>3.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.49</v>
+        <v>2.48</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.68</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>3.95</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.69</v>
+        <v>5.54</v>
       </c>
       <c r="O8" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="P8" t="n">
-        <v>4.2</v>
+        <v>1.47</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>5.54</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="P10" t="n">
-        <v>1.47</v>
+        <v>2.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="R10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC10" t="n">
         <v>2.63</v>
       </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.16</v>
-      </c>
       <c r="AD10" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.65</v>
+        <v>1.7</v>
       </c>
       <c r="O11" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,43 +2177,43 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>3.1</v>
       </c>
       <c r="U14" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V14" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W14" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
         <v>1.04</v>
@@ -2672,16 +2672,16 @@
         <v>4.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE14" t="n">
         <v>1.18</v>
@@ -2690,7 +2690,7 @@
         <v>1.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="P16" t="n">
-        <v>2.39</v>
+        <v>2.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.5</v>
+        <v>3.27</v>
       </c>
       <c r="R16" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="S16" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="T16" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U16" t="n">
-        <v>1.97</v>
+        <v>1.79</v>
       </c>
       <c r="V16" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.35</v>
+        <v>2.2</v>
       </c>
       <c r="O17" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>5.7</v>
+        <v>2.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="R17" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="S17" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="T17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z17" t="n">
-        <v>8.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.43</v>
+        <v>1.57</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="O18" t="n">
-        <v>3.88</v>
+        <v>4.25</v>
       </c>
       <c r="P18" t="n">
-        <v>1.93</v>
+        <v>5.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.27</v>
+        <v>1.83</v>
       </c>
       <c r="R18" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="S18" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T18" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="U18" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="V18" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="AE18" t="n">
         <v>1.48</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.32</v>
+        <v>2.43</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.15</v>
+        <v>1.89</v>
       </c>
       <c r="O5" t="n">
-        <v>6.6</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>13</v>
+        <v>3.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.49</v>
+        <v>2.48</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK5" t="n">
         <v>1.68</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>3.95</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.89</v>
+        <v>1.15</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="P6" t="n">
-        <v>3.45</v>
+        <v>13</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.48</v>
+        <v>1.49</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="S6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>2.63</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.68</v>
+        <v>3.95</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.04</v>
+        <v>1.7</v>
       </c>
       <c r="O9" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>1.78</v>
+        <v>4.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,10 +1859,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>4.04</v>
       </c>
       <c r="O10" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="R10" t="n">
         <v>2.28</v>
@@ -2018,43 +2018,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V10" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.7</v>
+        <v>2.65</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P11" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,43 +2177,43 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P13" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z13" t="n">
         <v>4.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AC13" t="n">
         <v>2.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z14" t="n">
         <v>4.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
         <v>2.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.2</v>
+        <v>1.35</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2.63</v>
+        <v>5.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="R17" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="S17" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="T17" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.88</v>
+        <v>1.52</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.42</v>
+        <v>1.11</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.57</v>
+        <v>2.43</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.35</v>
+        <v>2.2</v>
       </c>
       <c r="O18" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>5.9</v>
+        <v>2.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="S18" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="T18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z18" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.43</v>
+        <v>1.57</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.65</v>
+        <v>2.36</v>
       </c>
       <c r="O4" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="P4" t="n">
-        <v>3.05</v>
+        <v>3.44</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1361,61 +1361,61 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="O6" t="n">
-        <v>6.6</v>
+        <v>6.15</v>
       </c>
       <c r="P6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U6" t="n">
         <v>1.94</v>
       </c>
       <c r="V6" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
         <v>1.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AE6" t="n">
         <v>1.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AG6" t="n">
         <v>1.67</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5.54</v>
+        <v>4.04</v>
       </c>
       <c r="O8" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="P8" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="R8" t="n">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="V8" t="n">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.11</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.7</v>
+        <v>2.65</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P9" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.04</v>
+        <v>1.7</v>
       </c>
       <c r="O10" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>4.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.65</v>
+        <v>5.54</v>
       </c>
       <c r="O11" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>1.47</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>2.28</v>
+        <v>2.63</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,43 +2177,43 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="V11" t="n">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="W11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.11</v>
       </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z11" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.63</v>
+        <v>2.16</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.41</v>
+        <v>1.11</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,58 +2315,58 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O12" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="P12" t="n">
-        <v>5.35</v>
+        <v>5</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R12" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U12" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="V12" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.85</v>
+        <v>4.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF12" t="n">
         <v>1.75</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,37 +2474,37 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="O13" t="n">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.64</v>
+        <v>2.82</v>
       </c>
       <c r="R13" t="n">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="S13" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T13" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="U13" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="V13" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
         <v>1.16</v>
@@ -2513,25 +2513,25 @@
         <v>4.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC14" t="n">
         <v>2.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="O3" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="P3" t="n">
-        <v>2.97</v>
+        <v>3.44</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="O4" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="P4" t="n">
-        <v>3.44</v>
+        <v>2.97</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.04</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="R8" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U8" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.07</v>
+        <v>2.27</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.79</v>
+        <v>1.23</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.65</v>
+        <v>5.25</v>
       </c>
       <c r="O9" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>1.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.15</v>
+        <v>5.51</v>
       </c>
       <c r="R9" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U9" t="n">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="V9" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="W9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.11</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.41</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.7</v>
+        <v>4.04</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P10" t="n">
-        <v>4.3</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>5.54</v>
+        <v>1.7</v>
       </c>
       <c r="O11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P11" t="n">
         <v>4.3</v>
       </c>
-      <c r="P11" t="n">
-        <v>1.47</v>
-      </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,43 +2177,43 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,19 +2474,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="O13" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q13" t="n">
-        <v>2.82</v>
-      </c>
       <c r="R13" t="n">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="S13" t="n">
         <v>1.3</v>
@@ -2495,43 +2495,43 @@
         <v>3.16</v>
       </c>
       <c r="U13" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="V13" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W13" t="n">
         <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,19 +2633,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="R14" t="n">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="S14" t="n">
         <v>1.3</v>
@@ -2654,43 +2654,43 @@
         <v>3.16</v>
       </c>
       <c r="U14" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="V14" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W14" t="n">
         <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="O16" t="n">
-        <v>3.88</v>
+        <v>4.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.04</v>
+        <v>5.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.27</v>
+        <v>1.83</v>
       </c>
       <c r="R16" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="S16" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T16" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="V16" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="AE16" t="n">
         <v>1.48</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.36</v>
+        <v>2.43</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.35</v>
+        <v>2.2</v>
       </c>
       <c r="O17" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>5.9</v>
+        <v>2.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="R17" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="S17" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="T17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Z17" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.43</v>
+        <v>1.57</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="P18" t="n">
-        <v>2.63</v>
+        <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.5</v>
+        <v>3.27</v>
       </c>
       <c r="R18" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="S18" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="T18" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="V18" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O2" t="n">
         <v>2.7</v>
       </c>
-      <c r="O2" t="n">
-        <v>2.6</v>
-      </c>
       <c r="P2" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="P3" t="n">
-        <v>3.44</v>
+        <v>3.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="O4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF4" t="n">
         <v>2.7</v>
       </c>
-      <c r="P4" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,43 +1202,43 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="O5" t="n">
         <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S5" t="n">
         <v>1.33</v>
       </c>
       <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
         <v>2.75</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
         <v>1.26</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="AA5" t="n">
         <v>1.87</v>
@@ -1250,16 +1250,16 @@
         <v>3.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF5" t="n">
         <v>1.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,61 +1361,61 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="O6" t="n">
-        <v>6.15</v>
+        <v>6.05</v>
       </c>
       <c r="P6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="S6" t="n">
         <v>1.17</v>
       </c>
       <c r="T6" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="V6" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="W6" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AE6" t="n">
         <v>1.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AG6" t="n">
         <v>1.67</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>4.7</v>
+        <v>4.45</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1523,10 +1523,10 @@
         <v>1.55</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="P7" t="n">
-        <v>4.8</v>
+        <v>4.98</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="R8" t="n">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC8" t="n">
         <v>3.08</v>
       </c>
-      <c r="U8" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.59</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.27</v>
+        <v>1.93</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.41</v>
+        <v>1.79</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="P9" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.51</v>
+        <v>6.72</v>
       </c>
       <c r="R9" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="S9" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="U9" t="n">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="V9" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="W9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.13</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AK9" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>4.04</v>
+        <v>3.6</v>
       </c>
       <c r="O10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
         <v>4.1</v>
@@ -2012,49 +2012,49 @@
         <v>2.28</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U10" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V10" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.79</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
         <v>1.17</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.7</v>
+        <v>2.37</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2330,7 +2330,7 @@
         <v>2.25</v>
       </c>
       <c r="S12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T12" t="n">
         <v>3.12</v>
@@ -2348,25 +2348,25 @@
         <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.33</v>
+        <v>3.96</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
         <v>2.88</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF12" t="n">
         <v>1.75</v>
@@ -2477,10 +2477,10 @@
         <v>2.1</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" t="n">
         <v>2.62</v>
@@ -2501,7 +2501,7 @@
         <v>1.53</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
         <v>1.04</v>
@@ -2528,7 +2528,7 @@
         <v>1.18</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG13" t="n">
         <v>2.4</v>
@@ -2633,25 +2633,25 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.39</v>
+        <v>2.07</v>
       </c>
       <c r="O14" t="n">
-        <v>3.58</v>
+        <v>3.43</v>
       </c>
       <c r="P14" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="R14" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T14" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
         <v>2.41</v>
@@ -2663,7 +2663,7 @@
         <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
         <v>1.16</v>
@@ -2675,22 +2675,22 @@
         <v>1.66</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE14" t="n">
         <v>1.13</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>8.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="R15" t="n">
         <v>3.1</v>
@@ -2954,61 +2954,61 @@
         <v>1.35</v>
       </c>
       <c r="O16" t="n">
-        <v>4.25</v>
+        <v>4.7</v>
       </c>
       <c r="P16" t="n">
-        <v>5.9</v>
+        <v>4.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R16" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="S16" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T16" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="U16" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V16" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="W16" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="X16" t="n">
         <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Z16" t="n">
         <v>10</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.99</v>
+        <v>2.28</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="P17" t="n">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="R17" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="S17" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="T17" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="U17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V17" t="n">
         <v>2</v>
       </c>
-      <c r="V17" t="n">
-        <v>1.8</v>
-      </c>
       <c r="W17" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="O18" t="n">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>2.04</v>
+        <v>2.53</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.27</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="S18" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="T18" t="n">
-        <v>4.8</v>
+        <v>4.15</v>
       </c>
       <c r="U18" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="V18" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.2</v>
+        <v>7.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.11</v>
+        <v>1.87</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3434,7 +3434,7 @@
         <v>3.7</v>
       </c>
       <c r="P19" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.83</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T8" t="n">
         <v>3.28</v>
       </c>
-      <c r="P8" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U8" t="n">
-        <v>2.73</v>
+        <v>2.24</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.85</v>
+        <v>2.37</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.08</v>
+        <v>2.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.79</v>
+        <v>1.09</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>2.37</v>
       </c>
       <c r="O9" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.72</v>
+        <v>2.91</v>
       </c>
       <c r="R9" t="n">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="S9" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T9" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="U9" t="n">
-        <v>2.24</v>
+        <v>2.47</v>
       </c>
       <c r="V9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.57</v>
       </c>
-      <c r="W9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.09</v>
+        <v>1.47</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.37</v>
+        <v>1.83</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.91</v>
+        <v>2.42</v>
       </c>
       <c r="R11" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="S11" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="T11" t="n">
-        <v>3.02</v>
+        <v>2.63</v>
       </c>
       <c r="U11" t="n">
-        <v>2.47</v>
+        <v>2.73</v>
       </c>
       <c r="V11" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.76</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AG11" t="n">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>1.24</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.47</v>
+        <v>1.79</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="O13" t="n">
-        <v>3.22</v>
+        <v>3.43</v>
       </c>
       <c r="P13" t="n">
-        <v>2.9</v>
+        <v>2.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R13" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T13" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="U13" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="V13" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="O14" t="n">
-        <v>3.43</v>
+        <v>3.22</v>
       </c>
       <c r="P14" t="n">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="R14" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="S14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T14" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="U14" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="V14" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2801,7 +2801,7 @@
         <v>8.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="R15" t="n">
         <v>3.1</v>
@@ -2816,7 +2816,7 @@
         <v>1.67</v>
       </c>
       <c r="V15" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="W15" t="n">
         <v>1.25</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="O16" t="n">
-        <v>4.7</v>
+        <v>3.88</v>
       </c>
       <c r="P16" t="n">
-        <v>4.35</v>
+        <v>1.91</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.85</v>
+        <v>2.95</v>
       </c>
       <c r="R16" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="S16" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T16" t="n">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="V16" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="W16" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z16" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.6</v>
+        <v>1.36</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="O17" t="n">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="T17" t="n">
-        <v>5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.79</v>
-      </c>
       <c r="V17" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.2</v>
+        <v>7.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.11</v>
+        <v>1.87</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R18" t="n">
+        <v>3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD18" t="n">
         <v>2.02</v>
       </c>
-      <c r="O18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T18" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.62</v>
+        <v>2.6</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,22 +884,22 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="P3" t="n">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="S3" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="T3" t="n">
         <v>2.05</v>
@@ -914,34 +914,34 @@
         <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AE3" t="n">
         <v>1.01</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AK3" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.5</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,22 +1043,22 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="O4" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="P4" t="n">
-        <v>2.77</v>
+        <v>3.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="S4" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="T4" t="n">
         <v>2.05</v>
@@ -1073,50 +1073,50 @@
         <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AE4" t="n">
         <v>1.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AG4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
         <v>1.4</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AK4" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.91</v>
+        <v>1.12</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>6.05</v>
       </c>
       <c r="P5" t="n">
-        <v>3.4</v>
+        <v>16</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.47</v>
+        <v>1.55</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="S5" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>2.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.15</v>
+        <v>1.96</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.29</v>
+        <v>1.74</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>2.11</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.75</v>
+        <v>4.45</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.12</v>
+        <v>1.91</v>
       </c>
       <c r="O6" t="n">
-        <v>6.05</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>16</v>
+        <v>3.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.55</v>
+        <v>2.47</v>
       </c>
       <c r="R6" t="n">
-        <v>2.59</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.2</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AK6" t="n">
-        <v>4.45</v>
+        <v>1.75</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.37</v>
+        <v>3.6</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U9" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q9" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.47</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.76</v>
+        <v>4.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.6</v>
+        <v>2.37</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.1</v>
+        <v>2.91</v>
       </c>
       <c r="R10" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S10" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T10" t="n">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U10" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V10" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.2</v>
+        <v>3.76</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="O13" t="n">
-        <v>3.43</v>
+        <v>3.22</v>
       </c>
       <c r="P13" t="n">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="R13" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="S13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T13" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="U13" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="V13" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="O14" t="n">
-        <v>3.22</v>
+        <v>3.43</v>
       </c>
       <c r="P14" t="n">
-        <v>2.9</v>
+        <v>2.48</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R14" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T14" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="V14" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="O16" t="n">
-        <v>3.88</v>
+        <v>4.7</v>
       </c>
       <c r="P16" t="n">
-        <v>1.91</v>
+        <v>4.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.95</v>
+        <v>1.92</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="S16" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T16" t="n">
-        <v>5</v>
+        <v>4.45</v>
       </c>
       <c r="U16" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="V16" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="W16" t="n">
         <v>1.29</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.36</v>
+        <v>2.6</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="P17" t="n">
-        <v>2.53</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="R17" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="S17" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="T17" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.67</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.35</v>
+        <v>2.02</v>
       </c>
       <c r="O18" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>4.35</v>
+        <v>2.53</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="S18" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T18" t="n">
-        <v>4.45</v>
+        <v>4.15</v>
       </c>
       <c r="U18" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="V18" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3434,7 +3434,7 @@
         <v>3.7</v>
       </c>
       <c r="P19" t="n">
-        <v>5.95</v>
+        <v>5.8</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.12</v>
+        <v>1.91</v>
       </c>
       <c r="O5" t="n">
-        <v>6.05</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>16</v>
+        <v>3.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.55</v>
+        <v>2.47</v>
       </c>
       <c r="R5" t="n">
-        <v>2.59</v>
+        <v>2.1</v>
       </c>
       <c r="S5" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>2.06</v>
+        <v>2.75</v>
       </c>
       <c r="V5" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.2</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AK5" t="n">
-        <v>4.45</v>
+        <v>1.75</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.91</v>
+        <v>1.12</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>6.05</v>
       </c>
       <c r="P6" t="n">
-        <v>3.4</v>
+        <v>16</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.47</v>
+        <v>1.55</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="S6" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.87</v>
+        <v>1.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>2.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.15</v>
+        <v>1.96</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.29</v>
+        <v>1.74</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>2.11</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.75</v>
+        <v>4.45</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.72</v>
+        <v>2.91</v>
       </c>
       <c r="R8" t="n">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T8" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="U8" t="n">
-        <v>2.24</v>
+        <v>2.47</v>
       </c>
       <c r="V8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.57</v>
       </c>
-      <c r="W8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.09</v>
+        <v>1.47</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.37</v>
+        <v>1.83</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.91</v>
+        <v>2.42</v>
       </c>
       <c r="R10" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="S10" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="T10" t="n">
-        <v>3.02</v>
+        <v>2.63</v>
       </c>
       <c r="U10" t="n">
-        <v>2.47</v>
+        <v>2.73</v>
       </c>
       <c r="V10" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.76</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AG10" t="n">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>1.24</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.47</v>
+        <v>1.79</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.83</v>
+        <v>6</v>
       </c>
       <c r="O11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T11" t="n">
         <v>3.28</v>
       </c>
-      <c r="P11" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U11" t="n">
-        <v>2.73</v>
+        <v>2.24</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>2.37</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.08</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.79</v>
+        <v>1.09</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="O13" t="n">
-        <v>3.22</v>
+        <v>3.43</v>
       </c>
       <c r="P13" t="n">
-        <v>2.9</v>
+        <v>2.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R13" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T13" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="U13" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="V13" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="O14" t="n">
-        <v>3.43</v>
+        <v>3.22</v>
       </c>
       <c r="P14" t="n">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="R14" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="S14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T14" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="U14" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="V14" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.35</v>
+        <v>2.02</v>
       </c>
       <c r="O16" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>4.35</v>
+        <v>2.53</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="S16" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T16" t="n">
-        <v>4.45</v>
+        <v>4.15</v>
       </c>
       <c r="U16" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="V16" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Z16" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="O17" t="n">
-        <v>3.88</v>
+        <v>4.7</v>
       </c>
       <c r="P17" t="n">
-        <v>1.91</v>
+        <v>4.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.95</v>
+        <v>1.92</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="S17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T17" t="n">
-        <v>5</v>
+        <v>4.45</v>
       </c>
       <c r="U17" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="V17" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="W17" t="n">
         <v>1.29</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.36</v>
+        <v>2.6</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="P18" t="n">
-        <v>2.53</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="R18" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="S18" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="T18" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="V18" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK18" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.67</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,22 +884,22 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="P3" t="n">
-        <v>2.77</v>
+        <v>3.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="S3" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="T3" t="n">
         <v>2.05</v>
@@ -914,50 +914,50 @@
         <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AE3" t="n">
         <v>1.01</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AG3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
         <v>1.4</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AK3" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,22 +1043,22 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="O4" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="P4" t="n">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="S4" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="T4" t="n">
         <v>2.05</v>
@@ -1073,34 +1073,34 @@
         <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AE4" t="n">
         <v>1.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AK4" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.5</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,46 +1202,46 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
         <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="R5" t="n">
         <v>2.1</v>
       </c>
       <c r="S5" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="U5" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
         <v>1.26</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AB5" t="n">
         <v>1.77</v>
@@ -1250,16 +1250,16 @@
         <v>3.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF5" t="n">
         <v>1.7</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="O6" t="n">
-        <v>6.05</v>
+        <v>6.45</v>
       </c>
       <c r="P6" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="R6" t="n">
-        <v>2.59</v>
+        <v>3.1</v>
       </c>
       <c r="S6" t="n">
         <v>1.17</v>
@@ -1394,19 +1394,19 @@
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z6" t="n">
         <v>5.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
         <v>1.74</v>
@@ -1434,7 +1434,7 @@
         <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>4.45</v>
+        <v>3.95</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O7" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>4.98</v>
+        <v>5</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>1.83</v>
       </c>
       <c r="O8" t="n">
         <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.91</v>
+        <v>2.4</v>
       </c>
       <c r="R8" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="S8" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="T8" t="n">
-        <v>3.02</v>
+        <v>2.63</v>
       </c>
       <c r="U8" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.76</v>
+        <v>3.45</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AG8" t="n">
-        <v>2.23</v>
+        <v>1.9</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.47</v>
+        <v>1.85</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>2.33</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.1</v>
+        <v>2.88</v>
       </c>
       <c r="R9" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U9" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V9" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.2</v>
+        <v>3.76</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.83</v>
+        <v>3.11</v>
       </c>
       <c r="O10" t="n">
-        <v>3.28</v>
+        <v>3.56</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>1.84</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.42</v>
+        <v>4.1</v>
       </c>
       <c r="R10" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="S10" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T10" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="U10" t="n">
         <v>2.73</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
         <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB10" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC10" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AD10" t="n">
         <v>1.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.79</v>
+        <v>1.17</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2159,61 +2159,61 @@
         <v>6</v>
       </c>
       <c r="O11" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="P11" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.72</v>
+        <v>6.85</v>
       </c>
       <c r="R11" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="S11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T11" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="U11" t="n">
-        <v>2.24</v>
+        <v>2.47</v>
       </c>
       <c r="V11" t="n">
         <v>1.57</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.14</v>
       </c>
-      <c r="Z11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="AG11" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AK11" t="n">
         <v>1.09</v>
@@ -2318,58 +2318,58 @@
         <v>1.5</v>
       </c>
       <c r="O12" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="R12" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S12" t="n">
         <v>1.28</v>
       </c>
       <c r="T12" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="U12" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="V12" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W12" t="n">
         <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.96</v>
+        <v>4.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG12" t="n">
         <v>1.95</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="O13" t="n">
-        <v>3.43</v>
+        <v>3.22</v>
       </c>
       <c r="P13" t="n">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="R13" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="S13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T13" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="U13" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="V13" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="O14" t="n">
-        <v>3.22</v>
+        <v>3.43</v>
       </c>
       <c r="P14" t="n">
-        <v>2.9</v>
+        <v>2.48</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R14" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T14" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="V14" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="P16" t="n">
-        <v>2.53</v>
+        <v>2.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="S16" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="T16" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.63</v>
+        <v>3.48</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK16" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.67</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3119,16 +3119,16 @@
         <v>4.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R17" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="S17" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="T17" t="n">
-        <v>4.45</v>
+        <v>5.75</v>
       </c>
       <c r="U17" t="n">
         <v>1.65</v>
@@ -3137,37 +3137,37 @@
         <v>2.2</v>
       </c>
       <c r="W17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X17" t="n">
         <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z17" t="n">
         <v>10</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AB17" t="n">
         <v>4.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.02</v>
+        <v>2.58</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.75</v>
+        <v>3.32</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="O18" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="P18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="T18" t="n">
-        <v>5</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.79</v>
-      </c>
       <c r="V18" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.2</v>
+        <v>6.65</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.11</v>
+        <v>1.87</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3434,7 +3434,7 @@
         <v>3.7</v>
       </c>
       <c r="P19" t="n">
-        <v>5.8</v>
+        <v>5.95</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="O2" t="n">
         <v>2.7</v>
       </c>
       <c r="P2" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="S2" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="T2" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="U2" t="n">
-        <v>3.94</v>
+        <v>4.1</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
         <v>1.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AB2" t="n">
         <v>1.36</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="AD2" t="n">
         <v>1.08</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,61 +884,61 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="O3" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="P3" t="n">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.4</v>
+        <v>3.98</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="S3" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="T3" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="U3" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1.13</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.08</v>
+        <v>1.74</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="AB3" t="n">
         <v>1.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AG3" t="n">
         <v>1.47</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,28 +1043,28 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="O4" t="n">
         <v>2.6</v>
       </c>
       <c r="P4" t="n">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="S4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="T4" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="U4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="V4" t="n">
         <v>1.17</v>
@@ -1073,34 +1073,34 @@
         <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>1.14</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>6.45</v>
       </c>
       <c r="P5" t="n">
-        <v>3.75</v>
+        <v>17.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.4</v>
+        <v>1.49</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="S5" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="T5" t="n">
-        <v>2.71</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
-        <v>2.83</v>
+        <v>2.06</v>
       </c>
       <c r="V5" t="n">
-        <v>1.34</v>
+        <v>1.66</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.93</v>
+        <v>1.36</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>3</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.25</v>
+        <v>1.74</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.05</v>
+        <v>1.27</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>2.11</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.75</v>
+        <v>3.95</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.14</v>
+        <v>1.85</v>
       </c>
       <c r="O6" t="n">
-        <v>6.45</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>17.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.49</v>
+        <v>2.4</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>2.71</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>2.83</v>
       </c>
       <c r="V6" t="n">
-        <v>1.66</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.2</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AK6" t="n">
-        <v>3.95</v>
+        <v>1.75</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.33</v>
+        <v>3.11</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="P9" t="n">
-        <v>2.62</v>
+        <v>1.84</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="R9" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.25</v>
       </c>
-      <c r="T9" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.19</v>
-      </c>
       <c r="Z9" t="n">
-        <v>3.76</v>
+        <v>3.34</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.19</v>
+        <v>1.96</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.11</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>3.56</v>
+        <v>4.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.84</v>
+        <v>1.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.1</v>
+        <v>6.85</v>
       </c>
       <c r="R10" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="S10" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="U10" t="n">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="V10" t="n">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.34</v>
+        <v>4.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.05</v>
+        <v>2.64</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>6</v>
+        <v>2.33</v>
       </c>
       <c r="O11" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.4</v>
+        <v>2.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.85</v>
+        <v>2.88</v>
       </c>
       <c r="R11" t="n">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3.45</v>
+        <v>3.02</v>
       </c>
       <c r="U11" t="n">
         <v>2.47</v>
       </c>
       <c r="V11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.57</v>
       </c>
-      <c r="W11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.87</v>
+        <v>2.19</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.09</v>
+        <v>1.47</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>3.22</v>
       </c>
       <c r="P13" t="n">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="Q13" t="n">
         <v>2.62</v>
@@ -2498,7 +2498,7 @@
         <v>2.38</v>
       </c>
       <c r="V13" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W13" t="n">
         <v>1.1</v>
@@ -2507,19 +2507,19 @@
         <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.5</v>
+        <v>4.68</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB13" t="n">
         <v>2.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="AD13" t="n">
         <v>1.48</v>
@@ -2528,10 +2528,10 @@
         <v>1.18</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>1.33</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2633,16 +2633,16 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.43</v>
+        <v>3.35</v>
       </c>
       <c r="P14" t="n">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="R14" t="n">
         <v>2.24</v>
@@ -2651,46 +2651,46 @@
         <v>1.28</v>
       </c>
       <c r="T14" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="V14" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="W14" t="n">
         <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
         <v>1.16</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA14" t="n">
         <v>1.66</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE14" t="n">
         <v>1.13</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="O16" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="P16" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
-        <v>2.83</v>
+        <v>2.72</v>
       </c>
       <c r="S16" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T16" t="n">
-        <v>5</v>
+        <v>4.15</v>
       </c>
       <c r="U16" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="V16" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.2</v>
+        <v>6.65</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.11</v>
+        <v>1.87</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.48</v>
+        <v>2.63</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="O18" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="P18" t="n">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="R18" t="n">
-        <v>2.72</v>
+        <v>2.83</v>
       </c>
       <c r="S18" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T18" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="V18" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="W18" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.65</v>
+        <v>4.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.63</v>
+        <v>3.48</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK18" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.67</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -731,7 +731,7 @@
         <v>2.7</v>
       </c>
       <c r="P2" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="Q2" t="n">
         <v>3.4</v>
@@ -746,22 +746,22 @@
         <v>2.15</v>
       </c>
       <c r="U2" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="V2" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AA2" t="n">
         <v>3</v>
@@ -770,19 +770,19 @@
         <v>1.36</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.2</v>
+        <v>5.95</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE2" t="n">
         <v>1.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,80 +884,80 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.78</v>
+        <v>2.37</v>
       </c>
       <c r="O3" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="P3" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.98</v>
+        <v>3.24</v>
       </c>
       <c r="R3" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="S3" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="T3" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="AB3" t="n">
         <v>1.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AE3" t="n">
         <v>1.02</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="AG3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK3" t="n">
         <v>1.47</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.31</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="O4" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="P4" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.2</v>
+        <v>3.98</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="S4" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="T4" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="U4" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AE4" t="n">
         <v>1.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.14</v>
+        <v>1.85</v>
       </c>
       <c r="O5" t="n">
-        <v>6.45</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>17.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.49</v>
+        <v>2.4</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="S5" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>2.71</v>
       </c>
       <c r="U5" t="n">
-        <v>2.06</v>
+        <v>2.83</v>
       </c>
       <c r="V5" t="n">
-        <v>1.66</v>
+        <v>1.34</v>
       </c>
       <c r="W5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.2</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AK5" t="n">
-        <v>3.95</v>
+        <v>1.75</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.85</v>
+        <v>1.14</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>6.45</v>
       </c>
       <c r="P6" t="n">
-        <v>3.75</v>
+        <v>17.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.4</v>
+        <v>1.49</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="S6" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="T6" t="n">
-        <v>2.71</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
-        <v>2.83</v>
+        <v>2.06</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>1.66</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.93</v>
+        <v>1.36</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.77</v>
+        <v>3</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>1.74</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.05</v>
+        <v>1.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>2.11</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.75</v>
+        <v>3.95</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.11</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>3.56</v>
+        <v>4.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.84</v>
+        <v>1.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.1</v>
+        <v>6.85</v>
       </c>
       <c r="R9" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="S9" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="U9" t="n">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="V9" t="n">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.34</v>
+        <v>4.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.05</v>
+        <v>2.64</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>2.33</v>
       </c>
       <c r="O10" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4</v>
+        <v>2.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.85</v>
+        <v>2.88</v>
       </c>
       <c r="R10" t="n">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>3.45</v>
+        <v>3.02</v>
       </c>
       <c r="U10" t="n">
         <v>2.47</v>
       </c>
       <c r="V10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.57</v>
       </c>
-      <c r="W10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.87</v>
+        <v>2.19</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.09</v>
+        <v>1.47</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.33</v>
+        <v>3.11</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="P11" t="n">
-        <v>2.62</v>
+        <v>1.84</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="R11" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.25</v>
       </c>
-      <c r="T11" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.19</v>
-      </c>
       <c r="Z11" t="n">
-        <v>3.76</v>
+        <v>3.34</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.19</v>
+        <v>1.96</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.02</v>
+        <v>1.35</v>
       </c>
       <c r="O16" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="P16" t="n">
-        <v>2.75</v>
+        <v>4.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="R16" t="n">
-        <v>2.72</v>
+        <v>3.22</v>
       </c>
       <c r="S16" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="T16" t="n">
-        <v>4.15</v>
+        <v>5.75</v>
       </c>
       <c r="U16" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="W16" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
         <v>1.05</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.65</v>
+        <v>10</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.87</v>
+        <v>1.49</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.87</v>
+        <v>2.58</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.63</v>
+        <v>3.32</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.35</v>
+        <v>2.02</v>
       </c>
       <c r="O17" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="P17" t="n">
-        <v>4.35</v>
+        <v>2.75</v>
       </c>
       <c r="Q17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.91</v>
       </c>
-      <c r="R17" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="T17" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.65</v>
-      </c>
       <c r="V17" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
         <v>1.05</v>
       </c>
       <c r="Z17" t="n">
-        <v>10</v>
+        <v>6.65</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.49</v>
+        <v>1.87</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.58</v>
+        <v>1.87</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.32</v>
+        <v>2.63</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -804,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46189.29166666666</v>
@@ -893,16 +893,16 @@
         <v>3.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="S3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="T3" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="U3" t="n">
         <v>4.05</v>
@@ -911,25 +911,25 @@
         <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
         <v>1.12</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="AB3" t="n">
         <v>1.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AD3" t="n">
         <v>1.07</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O4" t="n">
-        <v>2.48</v>
+        <v>2.27</v>
       </c>
       <c r="P4" t="n">
         <v>2.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="R4" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="T4" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="U4" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="V4" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W4" t="n">
         <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Z4" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD4" t="n">
         <v>1.05</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AK4" t="n">
         <v>1.31</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.85</v>
+        <v>1.14</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>6.45</v>
       </c>
       <c r="P5" t="n">
-        <v>3.75</v>
+        <v>17.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.4</v>
+        <v>1.49</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="S5" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="T5" t="n">
-        <v>2.71</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
-        <v>2.83</v>
+        <v>2.06</v>
       </c>
       <c r="V5" t="n">
-        <v>1.34</v>
+        <v>1.66</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.93</v>
+        <v>1.36</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.77</v>
+        <v>3</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.25</v>
+        <v>1.74</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.05</v>
+        <v>1.27</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.7</v>
+        <v>2.11</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.75</v>
+        <v>3.95</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.14</v>
+        <v>1.85</v>
       </c>
       <c r="O6" t="n">
-        <v>6.45</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>17.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.49</v>
+        <v>2.4</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>2.71</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>2.83</v>
       </c>
       <c r="V6" t="n">
-        <v>1.66</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.2</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AK6" t="n">
-        <v>3.95</v>
+        <v>1.75</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.33</v>
+        <v>3.11</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="P10" t="n">
-        <v>2.62</v>
+        <v>1.84</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="R10" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.25</v>
       </c>
-      <c r="T10" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.19</v>
-      </c>
       <c r="Z10" t="n">
-        <v>3.76</v>
+        <v>3.34</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.19</v>
+        <v>1.96</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.11</v>
+        <v>2.33</v>
       </c>
       <c r="O11" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.84</v>
+        <v>2.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.1</v>
+        <v>2.88</v>
       </c>
       <c r="R11" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S11" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="U11" t="n">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="V11" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.34</v>
+        <v>3.76</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.96</v>
+        <v>2.19</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="P13" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="R13" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T13" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="U13" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.68</v>
+        <v>4.15</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="AD13" t="n">
         <v>1.48</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.55</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.67</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="O14" t="n">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="P14" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="R14" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="S14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="U14" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="V14" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.15</v>
+        <v>4.68</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="AD14" t="n">
         <v>1.48</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.35</v>
+        <v>2.02</v>
       </c>
       <c r="O16" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="P16" t="n">
-        <v>4.35</v>
+        <v>2.75</v>
       </c>
       <c r="Q16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.91</v>
       </c>
-      <c r="R16" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="T16" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.65</v>
-      </c>
       <c r="V16" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
         <v>1.05</v>
       </c>
       <c r="Z16" t="n">
-        <v>10</v>
+        <v>6.65</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.49</v>
+        <v>1.87</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.58</v>
+        <v>1.87</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.32</v>
+        <v>2.63</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="O17" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="P17" t="n">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="R17" t="n">
-        <v>2.72</v>
+        <v>2.83</v>
       </c>
       <c r="S17" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T17" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="W17" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.65</v>
+        <v>4.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.63</v>
+        <v>3.48</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.67</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,80 +3269,80 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R18" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK18" t="n">
         <v>2.4</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T18" t="n">
-        <v>5</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.36</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -880,7 +880,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46189.41666666666</v>
@@ -1023,23 +1023,23 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33', '48']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
@@ -1122,28 +1122,28 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46189.41666666666</v>
@@ -1198,35 +1198,35 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="O5" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="P5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="S5" t="n">
         <v>1.14</v>
       </c>
-      <c r="O5" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="P5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>3.1</v>
       </c>
-      <c r="S5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T5" t="n">
-        <v>4</v>
-      </c>
       <c r="U5" t="n">
-        <v>2.06</v>
+        <v>1.77</v>
       </c>
       <c r="V5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W5" t="n">
         <v>1.2</v>
@@ -1235,31 +1235,31 @@
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AB5" t="n">
         <v>3</v>
       </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="O8" t="n">
         <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="R8" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="S8" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>2.63</v>
+        <v>3.02</v>
       </c>
       <c r="U8" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="V8" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.45</v>
+        <v>3.76</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.11</v>
+        <v>1.83</v>
       </c>
       <c r="O10" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.84</v>
+        <v>3.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="S10" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T10" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="U10" t="n">
-        <v>2.73</v>
+        <v>2.48</v>
       </c>
       <c r="V10" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.17</v>
+        <v>1.85</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.33</v>
+        <v>3.11</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="P11" t="n">
-        <v>2.62</v>
+        <v>1.84</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="R11" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.25</v>
       </c>
-      <c r="T11" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.19</v>
-      </c>
       <c r="Z11" t="n">
-        <v>3.76</v>
+        <v>3.34</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.19</v>
+        <v>1.96</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2321,74 +2321,74 @@
         <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>4.9</v>
+        <v>5.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="R12" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="S12" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T12" t="n">
-        <v>3.14</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK12" t="n">
         <v>2.43</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2.32</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2788,35 +2788,35 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="P15" t="n">
-        <v>8.5</v>
+        <v>13.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="S15" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T15" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="U15" t="n">
         <v>1.67</v>
       </c>
       <c r="V15" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="W15" t="n">
         <v>1.25</v>
@@ -2834,16 +2834,16 @@
         <v>1.23</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.65</v>
+        <v>3.34</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AD15" t="n">
         <v>2.15</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AF15" t="n">
         <v>1.57</v>
@@ -2865,7 +2865,7 @@
         <v>1.12</v>
       </c>
       <c r="AK15" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.02</v>
+        <v>1.35</v>
       </c>
       <c r="O16" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="P16" t="n">
-        <v>2.75</v>
+        <v>4.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="R16" t="n">
-        <v>2.72</v>
+        <v>3.22</v>
       </c>
       <c r="S16" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="T16" t="n">
-        <v>4.15</v>
+        <v>5.75</v>
       </c>
       <c r="U16" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="W16" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
         <v>1.05</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.65</v>
+        <v>10</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.87</v>
+        <v>1.49</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.87</v>
+        <v>2.58</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.63</v>
+        <v>3.32</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="O17" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="P17" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="R17" t="n">
-        <v>2.83</v>
+        <v>2.72</v>
       </c>
       <c r="S17" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T17" t="n">
-        <v>5</v>
+        <v>4.15</v>
       </c>
       <c r="U17" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="V17" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.2</v>
+        <v>6.65</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.11</v>
+        <v>1.87</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.48</v>
+        <v>2.63</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="O18" t="n">
-        <v>4.7</v>
+        <v>3.88</v>
       </c>
       <c r="P18" t="n">
-        <v>4.35</v>
+        <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="R18" t="n">
-        <v>3.22</v>
+        <v>2.83</v>
       </c>
       <c r="S18" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="T18" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="V18" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="W18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z18" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.5</v>
+        <v>3.42</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.58</v>
+        <v>2.11</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.32</v>
+        <v>3.48</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O19" t="n">
         <v>3.7</v>
       </c>
       <c r="P19" t="n">
-        <v>5.95</v>
+        <v>5.7</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -852,31 +852,31 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.37</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="n">
-        <v>2.6</v>
+        <v>2.27</v>
       </c>
       <c r="P3" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="T3" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="U3" t="n">
-        <v>4.05</v>
+        <v>4.4</v>
       </c>
       <c r="V3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X3" t="n">
         <v>1.17</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.12</v>
-      </c>
       <c r="Y3" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -950,41 +950,41 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33', '48']</t>
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AP3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.52</v>
+        <v>1.42</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AS3" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="AT3" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46189.41666666666</v>
@@ -1011,139 +1011,139 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>['33', '48']</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>10</v>
-      </c>
       <c r="AP4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.42</v>
+        <v>0.52</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AS4" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="AT4" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46189.41666666666</v>
@@ -1357,50 +1357,50 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="O6" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="P6" t="n">
-        <v>3.75</v>
+        <v>4.01</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S6" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="T6" t="n">
-        <v>2.71</v>
+        <v>2.92</v>
       </c>
       <c r="U6" t="n">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB6" t="n">
         <v>1.77</v>
@@ -1409,16 +1409,16 @@
         <v>3.15</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1434,34 +1434,34 @@
         <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN6" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46189.5</v>
@@ -1497,36 +1497,36 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '90+1']</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
@@ -1599,28 +1599,28 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46189.52083333334</v>
@@ -1647,139 +1647,139 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.33</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.62</v>
+        <v>1.37</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.88</v>
+        <v>6.56</v>
       </c>
       <c r="R8" t="n">
-        <v>2.17</v>
+        <v>2.46</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T8" t="n">
-        <v>3.02</v>
+        <v>3.42</v>
       </c>
       <c r="U8" t="n">
-        <v>2.47</v>
+        <v>2.16</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="W8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>['20']</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>['34', '78']</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.11</v>
       </c>
-      <c r="X8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AK8" t="n">
-        <v>1.47</v>
+        <v>1.04</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN8" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO8" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46189.54166666666</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1834,111 +1834,111 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>2.24</v>
       </c>
       <c r="O9" t="n">
-        <v>4.33</v>
+        <v>3.35</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.85</v>
+        <v>2.8</v>
       </c>
       <c r="R9" t="n">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T9" t="n">
-        <v>3.45</v>
+        <v>3.02</v>
       </c>
       <c r="U9" t="n">
         <v>2.47</v>
       </c>
       <c r="V9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.57</v>
       </c>
-      <c r="W9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X9" t="n">
+      <c r="AG9" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46189.54166666666</v>
@@ -1974,33 +1974,33 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
         <v>3.7</v>
@@ -2009,95 +2009,95 @@
         <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>2.23</v>
+        <v>1.97</v>
       </c>
       <c r="S10" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>2.63</v>
+        <v>3.01</v>
       </c>
       <c r="U10" t="n">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="V10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE10" t="n">
         <v>1.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '64', '80']</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN10" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO10" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP10" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46189.54166666666</v>
@@ -2133,13 +2133,13 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -2152,17 +2152,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.11</v>
+        <v>3.99</v>
       </c>
       <c r="O11" t="n">
-        <v>3.56</v>
+        <v>3.75</v>
       </c>
       <c r="P11" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="Q11" t="n">
         <v>4.1</v>
@@ -2171,62 +2171,62 @@
         <v>2.28</v>
       </c>
       <c r="S11" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T11" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AE11" t="n">
         <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
+          <t>['8']</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ11" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK11" t="n">
         <v>1.17</v>
@@ -2235,28 +2235,28 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN11" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO11" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46189.54166666666</v>
@@ -2292,26 +2292,26 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2321,7 +2321,7 @@
         <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="Q12" t="n">
         <v>2.02</v>
@@ -2330,10 +2330,10 @@
         <v>2.31</v>
       </c>
       <c r="S12" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="U12" t="n">
         <v>2.31</v>
@@ -2348,35 +2348,35 @@
         <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
         <v>2.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE12" t="n">
         <v>1.13</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31', '35', '83']</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
@@ -2388,34 +2388,34 @@
         <v>1.15</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN12" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO12" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP12" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46189.5625</v>
@@ -2451,13 +2451,13 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2470,72 +2470,72 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="O13" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="P13" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="R13" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T13" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U13" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="V13" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '16']</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -2553,28 +2553,28 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN13" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO13" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP13" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AU13" s="3" t="n">
         <v>46189.58333333334</v>
@@ -2613,13 +2613,13 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2629,23 +2629,23 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O14" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.69</v>
+        <v>3.01</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="R14" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="S14" t="n">
         <v>1.3</v>
@@ -2654,86 +2654,86 @@
         <v>3.16</v>
       </c>
       <c r="U14" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
         <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.68</v>
+        <v>4.2</v>
       </c>
       <c r="AA14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>['34']</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.62</v>
       </c>
-      <c r="AB14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN14" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO14" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP14" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU14" s="3" t="n">
         <v>46189.58333333334</v>
@@ -2960,55 +2960,55 @@
         <v>4.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="R16" t="n">
-        <v>3.22</v>
+        <v>3.31</v>
       </c>
       <c r="S16" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="T16" t="n">
-        <v>5.75</v>
+        <v>4.45</v>
       </c>
       <c r="U16" t="n">
         <v>1.65</v>
       </c>
       <c r="V16" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X16" t="n">
         <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z16" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.58</v>
+        <v>2.1</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.32</v>
+        <v>2.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.4</v>
+        <v>2.68</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,31 +3110,31 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="O17" t="n">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="P17" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="Q17" t="n">
         <v>2.5</v>
       </c>
       <c r="R17" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="S17" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T17" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="W17" t="n">
         <v>1.22</v>
@@ -3143,28 +3143,28 @@
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.65</v>
+        <v>7</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AG17" t="n">
         <v>2.63</v>
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AK17" t="n">
         <v>1.67</v>
@@ -3269,31 +3269,31 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="O18" t="n">
-        <v>3.88</v>
+        <v>3.65</v>
       </c>
       <c r="P18" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="S18" t="n">
         <v>1.14</v>
       </c>
       <c r="T18" t="n">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="U18" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="V18" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="W18" t="n">
         <v>1.29</v>
@@ -3302,31 +3302,31 @@
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.42</v>
+        <v>3.79</v>
       </c>
       <c r="AC18" t="n">
         <v>1.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.48</v>
+        <v>3.56</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,19 +1647,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
         <v>1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -1668,10 +1668,10 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1679,107 +1679,107 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>['14', '64', '80']</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
         <v>6</v>
       </c>
-      <c r="O8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>['20']</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>['34', '78']</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>3</v>
-      </c>
       <c r="AN8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AO8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AP8" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.84</v>
+        <v>1.54</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.22</v>
+        <v>1.15</v>
       </c>
       <c r="AS8" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AT8" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46189.54166666666</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,22 +1806,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1838,107 +1838,107 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.24</v>
+        <v>3.99</v>
       </c>
       <c r="O9" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="P9" t="n">
-        <v>2.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="R9" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="S9" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T9" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="V9" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
         <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.78</v>
+        <v>3.42</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.66</v>
+        <v>2.89</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
+          <t>['8']</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.52</v>
+        <v>1.17</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AN9" t="n">
         <v>4</v>
       </c>
       <c r="AO9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP9" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AS9" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="AT9" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46189.54166666666</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,19 +1965,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -1986,10 +1986,10 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1997,107 +1997,107 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.85</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="P10" t="n">
-        <v>3.7</v>
+        <v>1.37</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>6.56</v>
       </c>
       <c r="R10" t="n">
-        <v>1.97</v>
+        <v>2.46</v>
       </c>
       <c r="S10" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="T10" t="n">
-        <v>3.01</v>
+        <v>3.42</v>
       </c>
       <c r="U10" t="n">
-        <v>2.75</v>
+        <v>2.16</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.34</v>
+        <v>5.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.81</v>
+        <v>1.48</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.88</v>
+        <v>2.46</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.83</v>
+        <v>2.14</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>['14', '64', '80']</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>['34', '78']</t>
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.83</v>
+        <v>1.04</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AN10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AO10" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AP10" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.54</v>
+        <v>0.84</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.15</v>
+        <v>2.22</v>
       </c>
       <c r="AS10" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AT10" t="n">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46189.54166666666</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -2156,68 +2156,68 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.99</v>
+        <v>2.24</v>
       </c>
       <c r="O11" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P11" t="n">
-        <v>1.71</v>
+        <v>2.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S11" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="U11" t="n">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W11" t="n">
         <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.42</v>
+        <v>3.78</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.89</v>
+        <v>2.66</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -2226,37 +2226,37 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.17</v>
+        <v>1.52</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN11" t="n">
         <v>4</v>
       </c>
       <c r="AO11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP11" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AS11" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="AT11" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46189.54166666666</v>
@@ -2442,25 +2442,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2474,107 +2474,107 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="O13" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.75</v>
+        <v>3.01</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.92</v>
+        <v>2.67</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="S13" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T13" t="n">
-        <v>3.6</v>
+        <v>3.16</v>
       </c>
       <c r="U13" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="V13" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
         <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF13" t="n">
         <v>1.51</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>['9', '16']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AN13" t="n">
         <v>2</v>
       </c>
       <c r="AO13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AP13" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.54</v>
+        <v>0.76</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.68</v>
+        <v>1.06</v>
       </c>
       <c r="AS13" t="n">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="AT13" t="n">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="AU13" s="3" t="n">
         <v>46189.58333333334</v>
@@ -2601,25 +2601,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2633,107 +2633,107 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P14" t="n">
-        <v>3.01</v>
+        <v>2.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.67</v>
+        <v>2.92</v>
       </c>
       <c r="R14" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T14" t="n">
-        <v>3.16</v>
+        <v>3.6</v>
       </c>
       <c r="U14" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V14" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
         <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF14" t="n">
         <v>1.51</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
+          <t>['9', '16']</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>['34']</t>
-        </is>
-      </c>
       <c r="AJ14" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AN14" t="n">
         <v>2</v>
       </c>
       <c r="AO14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AP14" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.76</v>
+        <v>1.54</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.06</v>
+        <v>1.68</v>
       </c>
       <c r="AS14" t="n">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="AT14" t="n">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="AU14" s="3" t="n">
         <v>46189.58333333334</v>
@@ -2919,22 +2919,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2947,111 +2947,111 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="O16" t="n">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="P16" t="n">
-        <v>4.35</v>
+        <v>2.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="R16" t="n">
-        <v>3.31</v>
+        <v>2.5</v>
       </c>
       <c r="S16" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="T16" t="n">
-        <v>4.45</v>
+        <v>4.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="V16" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="W16" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>['40']</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN16" t="n">
         <v>1</v>
       </c>
-      <c r="Y16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>-1</v>
-      </c>
       <c r="AO16" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP16" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU16" s="3" t="n">
         <v>46189.67708333334</v>
@@ -3078,139 +3078,139 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.05</v>
+        <v>1.45</v>
       </c>
       <c r="O17" t="n">
-        <v>3.84</v>
+        <v>4.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.53</v>
+        <v>5.63</v>
       </c>
       <c r="Q17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>['41', '73']</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK17" t="n">
         <v>2.5</v>
       </c>
-      <c r="R17" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T17" t="n">
-        <v>5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AL17" t="n">
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN17" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO17" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP17" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU17" s="3" t="n">
         <v>46189.67708333334</v>
@@ -3246,130 +3246,130 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="O18" t="n">
         <v>3.65</v>
       </c>
       <c r="P18" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R18" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="S18" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T18" t="n">
-        <v>4.85</v>
+        <v>5.25</v>
       </c>
       <c r="U18" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="V18" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Z18" t="n">
         <v>4.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.79</v>
+        <v>4.05</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AF18" t="n">
         <v>1.25</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29', '38', '64', '80']</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '6', '28', '54']</t>
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.17</v>
+        <v>1.62</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN18" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO18" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP18" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU18" s="3" t="n">
         <v>46189.67708333334</v>

--- a/jogos_2026-06-16.xlsx
+++ b/jogos_2026-06-16.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1198,111 +1198,111 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.13</v>
+        <v>1.76</v>
       </c>
       <c r="O5" t="n">
-        <v>6.65</v>
+        <v>3.52</v>
       </c>
       <c r="P5" t="n">
-        <v>18.5</v>
+        <v>4.01</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="R5" t="n">
-        <v>2.68</v>
+        <v>2.13</v>
       </c>
       <c r="S5" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="T5" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="U5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.77</v>
       </c>
-      <c r="V5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W5" t="n">
+      <c r="AC5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.2</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AK5" t="n">
-        <v>4.8</v>
+        <v>1.55</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46189.5</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1357,111 +1357,111 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.76</v>
+        <v>1.13</v>
       </c>
       <c r="O6" t="n">
-        <v>3.52</v>
+        <v>6.65</v>
       </c>
       <c r="P6" t="n">
-        <v>4.01</v>
+        <v>18.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="R6" t="n">
-        <v>2.13</v>
+        <v>2.68</v>
       </c>
       <c r="S6" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="T6" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>2.63</v>
+        <v>1.77</v>
       </c>
       <c r="V6" t="n">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AK6" t="n">
-        <v>1.55</v>
+        <v>4.8</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AN6" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AO6" t="n">
-        <v>16</v>
+        <v>-1</v>
       </c>
       <c r="AP6" t="n">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46189.5</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,28 +1647,28 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1679,25 +1679,25 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.85</v>
+        <v>3.99</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>3.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="S8" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T8" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
         <v>2.75</v>
@@ -1709,13 +1709,13 @@
         <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AA8" t="n">
         <v>1.81</v>
@@ -1724,62 +1724,62 @@
         <v>1.88</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>['14', '64', '80']</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.83</v>
+        <v>1.17</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AP8" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.15</v>
+        <v>2.25</v>
       </c>
       <c r="AS8" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AT8" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46189.54166666666</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,28 +1806,28 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
         <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1838,25 +1838,25 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.99</v>
+        <v>1.85</v>
       </c>
       <c r="O9" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>1.71</v>
+        <v>3.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="R9" t="n">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="S9" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="U9" t="n">
         <v>2.75</v>
@@ -1868,13 +1868,13 @@
         <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA9" t="n">
         <v>1.81</v>
@@ -1883,62 +1883,62 @@
         <v>1.88</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>['14', '64', '80']</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.17</v>
+        <v>1.83</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AP9" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.25</v>
+        <v>1.15</v>
       </c>
       <c r="AS9" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AT9" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46189.54166666666</v>
@@ -3078,139 +3078,139 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
         <v>2</v>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.45</v>
+        <v>2.72</v>
       </c>
       <c r="O17" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="P17" t="n">
-        <v>5.63</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.78</v>
+        <v>3.2</v>
       </c>
       <c r="R17" t="n">
-        <v>3.32</v>
+        <v>2.75</v>
       </c>
       <c r="S17" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="T17" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="V17" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="W17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>['29', '38', '64', '80']</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>['5', '6', '28', '54']</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.36</v>
       </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>['41', '73']</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AL17" t="n">
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AN17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AO17" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="AP17" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.16</v>
+        <v>2.71</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.12</v>
+        <v>2.25</v>
       </c>
       <c r="AS17" t="n">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="AT17" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="AU17" s="3" t="n">
         <v>46189.67708333334</v>
@@ -3237,139 +3237,139 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P18" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R18" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>['41', '73']</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
         <v>4</v>
       </c>
-      <c r="H18" t="n">
-        <v>4</v>
-      </c>
-      <c r="I18" t="n">
+      <c r="AN18" t="n">
         <v>2</v>
       </c>
-      <c r="J18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N18" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="T18" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>['29', '38', '64', '80']</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>['5', '6', '28', '54']</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
+      <c r="AO18" t="n">
         <v>9</v>
       </c>
-      <c r="AN18" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>22</v>
-      </c>
       <c r="AP18" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AQ18" t="n">
-        <v>2.71</v>
+        <v>1.16</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.25</v>
+        <v>1.12</v>
       </c>
       <c r="AS18" t="n">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="AT18" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="AU18" s="3" t="n">
         <v>46189.67708333334</v>
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O19" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P19" t="n">
-        <v>5.7</v>
+        <v>6.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
